--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_37.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2388899.266419164</v>
+        <v>2389970.390131441</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984941063</v>
+        <v>657188.6984941059</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984941063</v>
+        <v>657188.6984941059</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557205</v>
+        <v>81.99931295557391</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>1.798687867828961</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>87.3028355696476</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>133.6519859716245</v>
@@ -790,16 +790,16 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>322.1764561938114</v>
+        <v>173.0480995899248</v>
       </c>
       <c r="V3" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>5.146009903586577</v>
+        <v>3.347322035759929</v>
       </c>
       <c r="H5" t="n">
         <v>3.810231567849018</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.798687867826647</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>143.7261718927483</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>133.6519859716246</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.48881128536602</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796834</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.11157739633917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.347322035759929</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675665</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>307.4698632043681</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716246</v>
+        <v>238.2576915197132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536602</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796834</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225968</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1322,10 +1322,10 @@
         <v>91.79905402550071</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651275</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970477</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P10" t="n">
         <v>265.2018645413922</v>
@@ -1459,10 +1459,10 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>228.892412408888</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H12" t="n">
-        <v>5.544181526043773</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
         <v>498.2619859716245</v>
@@ -1498,7 +1498,7 @@
         <v>132.901311285366</v>
       </c>
       <c r="T12" t="n">
-        <v>402.1759444627968</v>
+        <v>233.8046879816496</v>
       </c>
       <c r="U12" t="n">
         <v>81.1584257979226</v>
@@ -1507,13 +1507,13 @@
         <v>95.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>100.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1614,10 +1614,10 @@
         <v>85.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>85.88962870801186</v>
+        <v>85.19354371151695</v>
       </c>
       <c r="G14" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H14" t="n">
         <v>73.89995518593948</v>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>192.7286559643715</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>28.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F15" t="n">
         <v>20.63624233787687</v>
@@ -1699,7 +1699,7 @@
         <v>5.950139648612248</v>
       </c>
       <c r="H15" t="n">
-        <v>5.544181526043773</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.2619859716246</v>
+        <v>402.2042587319001</v>
       </c>
       <c r="S15" t="n">
         <v>132.901311285366</v>
@@ -1738,10 +1738,10 @@
         <v>83.17594446279683</v>
       </c>
       <c r="U15" t="n">
-        <v>81.1584257979226</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W15" t="n">
         <v>113.3731429098285</v>
@@ -1750,7 +1750,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.305168319656873</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M16" t="n">
         <v>97.89093927140236</v>
@@ -1811,7 +1811,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S16" t="n">
-        <v>31.84005347334724</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>265.042185205795</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>5.950139648612264</v>
@@ -1978,16 +1978,16 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517959</v>
       </c>
       <c r="W18" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2091,7 +2091,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H20" t="n">
         <v>73.89995518593946</v>
@@ -2142,7 +2142,7 @@
         <v>319.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>272.5857484641728</v>
+        <v>273.2818334606677</v>
       </c>
       <c r="Y20" t="n">
         <v>192.3174326828064</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
         <v>28.93768689770263</v>
@@ -2173,7 +2173,7 @@
         <v>5.950139648612264</v>
       </c>
       <c r="H21" t="n">
-        <v>156.1729250448962</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>498.2619859716245</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
@@ -2215,16 +2215,16 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>100.8627394453875</v>
+        <v>323.805012205663</v>
       </c>
       <c r="Y21" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2267,7 +2267,7 @@
         <v>6.155529797123449</v>
       </c>
       <c r="M22" t="n">
-        <v>95.04057779393607</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2285,7 +2285,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S22" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U23" t="n">
-        <v>329.4071814013618</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V23" t="n">
         <v>310.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>319.3734759809475</v>
+        <v>318.6773909844526</v>
       </c>
       <c r="X23" t="n">
         <v>273.2818334606677</v>
@@ -2395,22 +2395,22 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H24" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,31 +2437,31 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>329.8907294904772</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S24" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T24" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U24" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V24" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517957</v>
       </c>
       <c r="W24" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
         <v>100.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M25" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N25" t="n">
         <v>150.9111244520127</v>
@@ -2519,10 +2519,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>28.98969199588089</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H26" t="n">
         <v>73.89995518593948</v>
@@ -2610,7 +2610,7 @@
         <v>330.1032663978569</v>
       </c>
       <c r="V26" t="n">
-        <v>310.8510241668239</v>
+        <v>310.1549391703289</v>
       </c>
       <c r="W26" t="n">
         <v>319.3734759809475</v>
@@ -2632,7 +2632,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>42.09991244551929</v>
+        <v>192.7286559643719</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -2641,7 +2641,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>5.950139648612248</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R27" t="n">
         <v>179.2619859716246</v>
@@ -2689,10 +2689,10 @@
         <v>81.1584257979226</v>
       </c>
       <c r="V27" t="n">
-        <v>318.4529399517957</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>100.8627394453875</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>6.155529797123435</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M28" t="n">
         <v>97.89093927140236</v>
@@ -2759,7 +2759,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S28" t="n">
-        <v>28.98969199588089</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2847,7 +2847,7 @@
         <v>330.1032663978569</v>
       </c>
       <c r="V29" t="n">
-        <v>310.1549391703289</v>
+        <v>310.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>319.3734759809475</v>
@@ -2856,7 +2856,7 @@
         <v>273.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>192.3174326828064</v>
+        <v>191.6213476863115</v>
       </c>
     </row>
     <row r="30">
@@ -2878,13 +2878,13 @@
         <v>23.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>324.9501396486123</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043758</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R30" t="n">
-        <v>498.2619859716245</v>
+        <v>329.890729490477</v>
       </c>
       <c r="S30" t="n">
-        <v>451.901311285366</v>
+        <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>233.8046879816494</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U30" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V30" t="n">
         <v>95.51066719152016</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.305168319657098</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -2993,10 +2993,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334727</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3106,19 +3106,19 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>28.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H33" t="n">
         <v>5.544181526043773</v>
@@ -3148,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
-        <v>402.2042587319001</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S33" t="n">
-        <v>132.901311285366</v>
+        <v>283.5300548042184</v>
       </c>
       <c r="T33" t="n">
         <v>83.17594446279683</v>
@@ -3163,13 +3163,13 @@
         <v>81.1584257979226</v>
       </c>
       <c r="V33" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
         <v>113.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>80.39139276613435</v>
@@ -3230,10 +3230,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364717</v>
       </c>
       <c r="S34" t="n">
-        <v>28.98969199588089</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84.99931295557451</v>
+        <v>81.69838314501889</v>
       </c>
       <c r="C35" t="n">
         <v>52.47457824299391</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>60.92708723799848</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
@@ -3352,13 +3352,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>172.5886009490645</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3385,16 +3385,16 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>374</v>
+        <v>101.2619859716246</v>
       </c>
       <c r="S36" t="n">
-        <v>374</v>
+        <v>54.90131128536602</v>
       </c>
       <c r="T36" t="n">
-        <v>211.1824455576123</v>
+        <v>5.175944462796835</v>
       </c>
       <c r="U36" t="n">
         <v>3.158425797922597</v>
@@ -3403,13 +3403,13 @@
         <v>17.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>374</v>
+        <v>35.37314290982852</v>
       </c>
       <c r="X36" t="n">
         <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.391392766134345</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37">
@@ -3513,7 +3513,7 @@
         <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2819954025941</v>
+        <v>1.981065592038484</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>60.92708723799848</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
@@ -3586,13 +3586,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3625,19 +3625,19 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
-        <v>374</v>
+        <v>101.2619859716246</v>
       </c>
       <c r="S39" t="n">
-        <v>54.90131128536602</v>
+        <v>184.1128930049607</v>
       </c>
       <c r="T39" t="n">
         <v>5.175944462796835</v>
       </c>
       <c r="U39" t="n">
-        <v>138.7925326551979</v>
+        <v>3.158425797922597</v>
       </c>
       <c r="V39" t="n">
-        <v>374</v>
+        <v>17.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>35.37314290982852</v>
@@ -3646,7 +3646,7 @@
         <v>22.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>374</v>
+        <v>2.391392766134345</v>
       </c>
     </row>
     <row r="40">
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>125.8743140373655</v>
       </c>
       <c r="T41" t="n">
         <v>287.2171194170061</v>
@@ -3801,7 +3801,7 @@
         <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>125.8743140373654</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>68.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>54.93768689770263</v>
+        <v>57.32446034312783</v>
       </c>
       <c r="E42" t="n">
         <v>49.67209722191262</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.386773445425144</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>205.2619859716246</v>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.581873503942997</v>
       </c>
       <c r="N43" t="n">
         <v>176.9111244520127</v>
@@ -3938,13 +3938,13 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>318.7418200305956</v>
+        <v>374</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3981,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>78.43193102812603</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>142.3134383061603</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>336.8510241668239</v>
@@ -4041,7 +4041,7 @@
         <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4163,7 +4163,7 @@
         <v>32.15552979712345</v>
       </c>
       <c r="M46" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>176.9111244520127</v>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>162.6953509620701</v>
+        <v>286.5862902334724</v>
       </c>
       <c r="S46" t="n">
         <v>57.84005347334727</v>
@@ -4297,49 +4297,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.7310038072345</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>58.75668234966486</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069325093</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398968</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>38.966708557008</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755353</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>31.73685643215047</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>770.4399999999999</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>834.5019149748742</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>385.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1125.74</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178447</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698512</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861907</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165467</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.183587413852</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190981</v>
       </c>
     </row>
     <row r="3">
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.13396963146437</v>
+        <v>1051.142534488436</v>
       </c>
       <c r="C3" t="n">
-        <v>33.13396963146437</v>
+        <v>1051.142534488436</v>
       </c>
       <c r="D3" t="n">
-        <v>33.13396963146437</v>
+        <v>1051.142534488436</v>
       </c>
       <c r="E3" t="n">
-        <v>33.13396963146437</v>
+        <v>705.0091029511505</v>
       </c>
       <c r="F3" t="n">
-        <v>33.13396963146437</v>
+        <v>361.9421914987495</v>
       </c>
       <c r="G3" t="n">
         <v>33.13396963146437</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1360.997993968056</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1297.877982568697</v>
       </c>
       <c r="T3" t="n">
-        <v>1146.820433372515</v>
+        <v>1293.359351798195</v>
       </c>
       <c r="U3" t="n">
-        <v>821.3896695403821</v>
+        <v>1118.563291606351</v>
       </c>
       <c r="V3" t="n">
-        <v>443.6118917626043</v>
+        <v>1103.906052018957</v>
       </c>
       <c r="W3" t="n">
-        <v>410.9117474092422</v>
+        <v>1071.205907665595</v>
       </c>
       <c r="X3" t="n">
-        <v>33.13396963146437</v>
+        <v>1051.142534488436</v>
       </c>
       <c r="Y3" t="n">
-        <v>33.13396963146437</v>
+        <v>1051.142534488436</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1359.924714679384</v>
+        <v>1004.107138046808</v>
       </c>
       <c r="C4" t="n">
-        <v>1359.924714679384</v>
+        <v>1031.234527536378</v>
       </c>
       <c r="D4" t="n">
-        <v>1359.924714679384</v>
+        <v>1144.553671661379</v>
       </c>
       <c r="E4" t="n">
-        <v>1359.924714679384</v>
+        <v>1262.382575872791</v>
       </c>
       <c r="F4" t="n">
-        <v>1359.924714679384</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G4" t="n">
-        <v>1359.924714679384</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H4" t="n">
-        <v>1359.924714679384</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>179.6001272851838</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>368.4538490669395</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>615.0149741642425</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="V4" t="n">
-        <v>813.8363670501885</v>
+        <v>458.0187904176125</v>
       </c>
       <c r="W4" t="n">
-        <v>985.7272853098659</v>
+        <v>629.9097086772899</v>
       </c>
       <c r="X4" t="n">
-        <v>1136.75807633406</v>
+        <v>780.9404997014834</v>
       </c>
       <c r="Y4" t="n">
-        <v>1248.167377013092</v>
+        <v>892.3498003805157</v>
       </c>
     </row>
     <row r="5">
@@ -4549,34 +4549,34 @@
         <v>38.96670855700565</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540305</v>
+        <v>35.58557518755118</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.73685643214813</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>263.0661931588676</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>327.128108133742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>697.388108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="D6" t="n">
-        <v>241.6095073802453</v>
+        <v>930.8098503699318</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>584.6764188326463</v>
       </c>
       <c r="F6" t="n">
         <v>241.6095073802453</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1115.008252590758</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>737.23047481298</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>732.7118440424781</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>732.5139391960917</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>717.8566996086976</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W6" t="n">
-        <v>685.1565552553354</v>
+        <v>1096.051174953907</v>
       </c>
       <c r="X6" t="n">
-        <v>307.3787774775576</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y6" t="n">
-        <v>241.6095073802453</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>348.3807442728818</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C7" t="n">
-        <v>348.3807442728818</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D7" t="n">
-        <v>461.6998883978819</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E7" t="n">
-        <v>579.5287926092949</v>
+        <v>761.2674835243668</v>
       </c>
       <c r="F7" t="n">
-        <v>703.8897652012304</v>
+        <v>885.6284561163022</v>
       </c>
       <c r="G7" t="n">
-        <v>857.4784261700829</v>
+        <v>1039.217117085155</v>
       </c>
       <c r="H7" t="n">
-        <v>1028.614002149153</v>
+        <v>1210.352693064224</v>
       </c>
       <c r="I7" t="n">
-        <v>1255.22297682294</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J7" t="n">
-        <v>1255.22297682294</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>149.5593513869358</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>149.5593513869358</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>348.3807442728818</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>348.3807442728818</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>348.3807442728818</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>348.3807442728818</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.7310038072321</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>58.75668234966251</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324858</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398732</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700565</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755118</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,16 +4795,16 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>263.0661931588676</v>
+        <v>29.92</v>
       </c>
       <c r="K8" t="n">
-        <v>633.3261931588676</v>
+        <v>400.18</v>
       </c>
       <c r="L8" t="n">
+        <v>464.2419149748744</v>
+      </c>
+      <c r="M8" t="n">
         <v>697.388108133742</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
         <v>1067.648108133742</v>
@@ -4828,19 +4828,19 @@
         <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>971.178558602</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183394</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486954</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460007</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512468</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1252.121695500138</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1189.001684100779</v>
       </c>
       <c r="T9" t="n">
-        <v>1143.60646374105</v>
+        <v>1184.483053330277</v>
       </c>
       <c r="U9" t="n">
-        <v>1143.408558894664</v>
+        <v>1184.28514848389</v>
       </c>
       <c r="V9" t="n">
-        <v>1128.75131930727</v>
+        <v>1169.627908896496</v>
       </c>
       <c r="W9" t="n">
-        <v>1096.051174953907</v>
+        <v>1136.927764543134</v>
       </c>
       <c r="X9" t="n">
-        <v>718.2733971761295</v>
+        <v>759.1499867653563</v>
       </c>
       <c r="Y9" t="n">
-        <v>340.4956193983517</v>
+        <v>381.3722089875785</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>774.8297405151413</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="C10" t="n">
-        <v>900.8317463335771</v>
+        <v>344.620323690067</v>
       </c>
       <c r="D10" t="n">
-        <v>1014.150890458577</v>
+        <v>457.9394678150671</v>
       </c>
       <c r="E10" t="n">
-        <v>1131.97979466999</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="F10" t="n">
-        <v>1256.340767261926</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>853.7180055872682</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4968,10 +4968,10 @@
         <v>1149.534310393385</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660643</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121328</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q10" t="n">
         <v>351.4672397226398</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="V10" t="n">
-        <v>228.741392885946</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="W10" t="n">
-        <v>400.6323111456234</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="X10" t="n">
-        <v>551.6631021698169</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="Y10" t="n">
-        <v>663.0724028488492</v>
+        <v>218.6183178716313</v>
       </c>
     </row>
     <row r="11">
@@ -5035,22 +5035,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K11" t="n">
-        <v>706.294305243247</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L11" t="n">
-        <v>936.7915875548047</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M11" t="n">
-        <v>1585.241587554806</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="N11" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O11" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P11" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q11" t="n">
         <v>2620</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>405.7156897352962</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C12" t="n">
-        <v>363.1905256489131</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D12" t="n">
-        <v>333.9605388835569</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E12" t="n">
-        <v>310.0493295684936</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F12" t="n">
-        <v>289.204640338315</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G12" t="n">
-        <v>58.00018335964018</v>
+        <v>380.2224055818624</v>
       </c>
       <c r="H12" t="n">
         <v>52.4</v>
@@ -5132,31 +5132,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R12" t="n">
-        <v>1810.695670043663</v>
+        <v>1737.651701112932</v>
       </c>
       <c r="S12" t="n">
-        <v>1676.451921270566</v>
+        <v>1603.407952339835</v>
       </c>
       <c r="T12" t="n">
-        <v>1270.213593530367</v>
+        <v>1367.241600843219</v>
       </c>
       <c r="U12" t="n">
-        <v>1188.235385653677</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V12" t="n">
-        <v>1091.759964248101</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W12" t="n">
-        <v>977.2416380765574</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X12" t="n">
-        <v>875.3600830812164</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y12" t="n">
-        <v>471.9344338224948</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="13">
@@ -5257,7 +5257,7 @@
         <v>297.2237316162127</v>
       </c>
       <c r="F14" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G14" t="n">
         <v>127.0464193797368</v>
@@ -5272,22 +5272,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K14" t="n">
-        <v>327.4727226113304</v>
+        <v>706.2943052432449</v>
       </c>
       <c r="L14" t="n">
-        <v>557.9700049228883</v>
+        <v>936.7915875548028</v>
       </c>
       <c r="M14" t="n">
-        <v>557.9700049228883</v>
+        <v>1585.241587554805</v>
       </c>
       <c r="N14" t="n">
-        <v>1165.464800116248</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O14" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P14" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>654.8939430267876</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C15" t="n">
         <v>460.2185329617658</v>
@@ -5333,13 +5333,13 @@
         <v>430.9885461964096</v>
       </c>
       <c r="E15" t="n">
-        <v>84.85511465912413</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F15" t="n">
-        <v>64.01042542894548</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964018</v>
+        <v>380.2224055818624</v>
       </c>
       <c r="H15" t="n">
         <v>52.4</v>
@@ -5369,31 +5369,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2059.873923335154</v>
+        <v>1907.723677356516</v>
       </c>
       <c r="S15" t="n">
-        <v>1925.630174562057</v>
+        <v>1773.479928583419</v>
       </c>
       <c r="T15" t="n">
-        <v>1841.614069044081</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U15" t="n">
-        <v>1759.635861167391</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V15" t="n">
-        <v>1340.938217539593</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W15" t="n">
-        <v>1226.419891368049</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X15" t="n">
-        <v>1124.538336372708</v>
+        <v>972.3880903940692</v>
       </c>
       <c r="Y15" t="n">
-        <v>1043.334909336209</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="16">
@@ -5433,25 +5433,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N16" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O16" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P16" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q16" t="n">
-        <v>466.2233328154397</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R16" t="n">
-        <v>84.56167017509823</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5506,25 +5506,25 @@
         <v>52.4</v>
       </c>
       <c r="J17" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K17" t="n">
-        <v>790.1259849731395</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L17" t="n">
-        <v>1438.575984973139</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M17" t="n">
-        <v>1585.241587554804</v>
+        <v>988.9116280297749</v>
       </c>
       <c r="N17" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O17" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P17" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q17" t="n">
         <v>2620</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1372.382356401963</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C18" t="n">
-        <v>1104.66297740621</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D18" t="n">
-        <v>753.2107684186319</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E18" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F18" t="n">
         <v>64.01042542894548</v>
@@ -5621,16 +5621,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y18" t="n">
-        <v>1438.601100489161</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="19">
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C20" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D20" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E20" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F20" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G20" t="n">
         <v>127.0464193797368</v>
@@ -5743,25 +5743,25 @@
         <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K20" t="n">
-        <v>790.1259849731395</v>
+        <v>1216.127674193434</v>
       </c>
       <c r="L20" t="n">
-        <v>1438.575984973139</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="M20" t="n">
-        <v>2087.025984973143</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="N20" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O20" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P20" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q20" t="n">
         <v>2620</v>
@@ -5785,10 +5785,10 @@
         <v>1242.451613120012</v>
       </c>
       <c r="X20" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>332.6717208045656</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C21" t="n">
-        <v>290.1465567181825</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D21" t="n">
-        <v>260.9165699528263</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E21" t="n">
-        <v>237.005360637763</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F21" t="n">
-        <v>216.1606714075843</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>210.150429338279</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5843,31 +5843,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1737.651701112932</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S21" t="n">
-        <v>1603.407952339835</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T21" t="n">
-        <v>1519.391846821859</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U21" t="n">
-        <v>1437.413638945169</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V21" t="n">
-        <v>1018.715995317371</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W21" t="n">
-        <v>581.9754469236045</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X21" t="n">
-        <v>480.0938919282636</v>
+        <v>1294.610312616292</v>
       </c>
       <c r="Y21" t="n">
-        <v>398.8904648917642</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="22">
@@ -5910,22 +5910,22 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N22" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O22" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P22" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q22" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5983,13 +5983,13 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K23" t="n">
-        <v>706.2943052432395</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L23" t="n">
-        <v>936.7915875547974</v>
+        <v>1020.623267284697</v>
       </c>
       <c r="M23" t="n">
-        <v>1585.241587554802</v>
+        <v>1669.073267284701</v>
       </c>
       <c r="N23" t="n">
         <v>2233.691587554807</v>
@@ -6013,10 +6013,10 @@
         <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
         <v>1243.154729278087</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1147.188141492593</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C24" t="n">
-        <v>1104.66297740621</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D24" t="n">
-        <v>753.2107684186319</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E24" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F24" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G24" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H24" t="n">
         <v>52.4</v>
@@ -6080,31 +6080,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1907.723677356515</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S24" t="n">
-        <v>1773.479928583418</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T24" t="n">
-        <v>1689.463823065442</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U24" t="n">
-        <v>1607.485615188752</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V24" t="n">
         <v>1511.010193783176</v>
       </c>
       <c r="W24" t="n">
-        <v>1396.491867611632</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X24" t="n">
-        <v>1294.610312616291</v>
+        <v>972.3880903940692</v>
       </c>
       <c r="Y24" t="n">
-        <v>1213.406885579792</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C25" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D25" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E25" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F25" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G25" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H25" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I25" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J25" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K25" t="n">
         <v>1597.372803794637</v>
@@ -6147,7 +6147,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M25" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N25" t="n">
         <v>1339.839881046618</v>
@@ -6162,7 +6162,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R25" t="n">
-        <v>81.68251716755645</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6171,19 +6171,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U25" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V25" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W25" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X25" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y25" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="26">
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C26" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D26" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F26" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G26" t="n">
         <v>127.0464193797368</v>
@@ -6220,13 +6220,13 @@
         <v>567.6776741934345</v>
       </c>
       <c r="K26" t="n">
-        <v>1216.127674193434</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L26" t="n">
-        <v>1864.577674193434</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M26" t="n">
-        <v>2233.691587554807</v>
+        <v>1632.421694143185</v>
       </c>
       <c r="N26" t="n">
         <v>2233.691587554807</v>
@@ -6253,16 +6253,16 @@
         <v>1879.04201730968</v>
       </c>
       <c r="V26" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W26" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X26" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="27">
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>824.9659192703713</v>
+        <v>1299.338387471232</v>
       </c>
       <c r="C27" t="n">
-        <v>782.4407551839881</v>
+        <v>1104.66297740621</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964096</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E27" t="n">
-        <v>84.85511465912413</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F27" t="n">
         <v>64.01042542894548</v>
@@ -6317,31 +6317,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R27" t="n">
-        <v>2132.917892265885</v>
+        <v>2059.873923335154</v>
       </c>
       <c r="S27" t="n">
-        <v>1998.674143492788</v>
+        <v>1925.630174562057</v>
       </c>
       <c r="T27" t="n">
-        <v>1914.658037974811</v>
+        <v>1841.614069044081</v>
       </c>
       <c r="U27" t="n">
-        <v>1832.679830098122</v>
+        <v>1759.635861167391</v>
       </c>
       <c r="V27" t="n">
-        <v>1511.010193783176</v>
+        <v>1663.160439761815</v>
       </c>
       <c r="W27" t="n">
-        <v>1074.26964538941</v>
+        <v>1548.642113590271</v>
       </c>
       <c r="X27" t="n">
-        <v>972.3880903940692</v>
+        <v>1446.76055859493</v>
       </c>
       <c r="Y27" t="n">
-        <v>891.1846633575699</v>
+        <v>1365.557131558431</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L28" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M28" t="n">
-        <v>1492.275360291075</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N28" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O28" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P28" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R28" t="n">
-        <v>81.68251716755645</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S28" t="n">
         <v>52.4</v>
@@ -6454,25 +6454,25 @@
         <v>52.4</v>
       </c>
       <c r="J29" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K29" t="n">
-        <v>1216.127674193434</v>
+        <v>706.294305243247</v>
       </c>
       <c r="L29" t="n">
-        <v>1446.624956504992</v>
+        <v>936.7915875548047</v>
       </c>
       <c r="M29" t="n">
-        <v>1637.361628029778</v>
+        <v>1585.241587554806</v>
       </c>
       <c r="N29" t="n">
-        <v>1637.361628029778</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O29" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P29" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q29" t="n">
         <v>2620</v>
@@ -6490,13 +6490,13 @@
         <v>1879.04201730968</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W29" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X29" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y29" t="n">
         <v>772.852440244275</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>502.743697048149</v>
+        <v>824.9659192703713</v>
       </c>
       <c r="C30" t="n">
-        <v>460.2185329617658</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D30" t="n">
-        <v>430.9885461964096</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E30" t="n">
-        <v>407.0773368813464</v>
+        <v>729.2995591035686</v>
       </c>
       <c r="F30" t="n">
         <v>386.2326476511677</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964016</v>
+        <v>380.2224055818624</v>
       </c>
       <c r="H30" t="n">
         <v>52.4</v>
@@ -6557,28 +6557,28 @@
         <v>2240.946636437805</v>
       </c>
       <c r="R30" t="n">
-        <v>1737.651701112932</v>
+        <v>1907.723677356516</v>
       </c>
       <c r="S30" t="n">
-        <v>1281.185730117613</v>
+        <v>1773.479928583419</v>
       </c>
       <c r="T30" t="n">
-        <v>1045.019378620997</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U30" t="n">
-        <v>963.0411707443078</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V30" t="n">
-        <v>866.5657493387318</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W30" t="n">
-        <v>752.0474231671878</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X30" t="n">
-        <v>650.1658681718469</v>
+        <v>972.3880903940692</v>
       </c>
       <c r="Y30" t="n">
-        <v>568.9624411353476</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="31">
@@ -6588,31 +6588,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H31" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K31" t="n">
         <v>1597.372803794637</v>
@@ -6633,10 +6633,10 @@
         <v>821.1953191039224</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154396</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017509824</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S31" t="n">
         <v>52.4</v>
@@ -6645,19 +6645,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V31" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X31" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="32">
@@ -6694,13 +6694,13 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K32" t="n">
-        <v>706.2943052432373</v>
+        <v>706.294305243247</v>
       </c>
       <c r="L32" t="n">
-        <v>936.7915875547951</v>
+        <v>936.7915875548047</v>
       </c>
       <c r="M32" t="n">
-        <v>1585.241587554801</v>
+        <v>1585.241587554806</v>
       </c>
       <c r="N32" t="n">
         <v>2233.691587554807</v>
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1147.188141492594</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C33" t="n">
-        <v>782.4407551839881</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D33" t="n">
-        <v>753.2107684186319</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E33" t="n">
         <v>407.0773368813464</v>
       </c>
       <c r="F33" t="n">
-        <v>64.01042542894548</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G33" t="n">
         <v>58.00018335964018</v>
@@ -6791,10 +6791,10 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R33" t="n">
-        <v>1907.723677356516</v>
+        <v>2059.873923335154</v>
       </c>
       <c r="S33" t="n">
         <v>1773.479928583419</v>
@@ -6806,16 +6806,16 @@
         <v>1607.485615188752</v>
       </c>
       <c r="V33" t="n">
-        <v>1511.010193783176</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W33" t="n">
-        <v>1396.491867611632</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X33" t="n">
-        <v>1294.610312616291</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y33" t="n">
-        <v>1213.406885579792</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="34">
@@ -6873,7 +6873,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R34" t="n">
-        <v>81.68251716755645</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
@@ -6937,7 +6937,7 @@
         <v>535.4900049228883</v>
       </c>
       <c r="M35" t="n">
-        <v>739.431587554807</v>
+        <v>905.7500049228884</v>
       </c>
       <c r="N35" t="n">
         <v>1109.691587554807</v>
@@ -6955,25 +6955,25 @@
         <v>1496</v>
       </c>
       <c r="S35" t="n">
-        <v>1434.457487638385</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T35" t="n">
-        <v>1249.38969024747</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U35" t="n">
-        <v>994.7399262092307</v>
+        <v>991.405653673316</v>
       </c>
       <c r="V35" t="n">
-        <v>759.5368714952672</v>
+        <v>756.2025989593525</v>
       </c>
       <c r="W35" t="n">
-        <v>515.7252795953201</v>
+        <v>512.3910070594054</v>
       </c>
       <c r="X35" t="n">
-        <v>318.4709023623224</v>
+        <v>315.1366298264077</v>
       </c>
       <c r="Y35" t="n">
-        <v>202.9987481372655</v>
+        <v>199.6644756013507</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.92</v>
+        <v>875.5512958944987</v>
       </c>
       <c r="C36" t="n">
-        <v>29.92</v>
+        <v>875.5512958944987</v>
       </c>
       <c r="D36" t="n">
-        <v>29.92</v>
+        <v>875.5512958944987</v>
       </c>
       <c r="E36" t="n">
-        <v>29.92</v>
+        <v>875.5512958944987</v>
       </c>
       <c r="F36" t="n">
-        <v>29.92</v>
+        <v>532.4843844420977</v>
       </c>
       <c r="G36" t="n">
-        <v>29.92</v>
+        <v>204.2519201505702</v>
       </c>
       <c r="H36" t="n">
         <v>29.92</v>
@@ -7007,16 +7007,16 @@
         <v>29.92</v>
       </c>
       <c r="J36" t="n">
-        <v>29.92</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K36" t="n">
-        <v>345.3082935472136</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L36" t="n">
-        <v>567.4798694413171</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M36" t="n">
-        <v>851.5752611841763</v>
+        <v>884.0224426446173</v>
       </c>
       <c r="N36" t="n">
         <v>1188.111259659669</v>
@@ -7028,31 +7028,31 @@
         <v>1496</v>
       </c>
       <c r="Q36" t="n">
-        <v>1422.95603106927</v>
+        <v>1496</v>
       </c>
       <c r="R36" t="n">
-        <v>1045.178253291492</v>
+        <v>1393.715165685228</v>
       </c>
       <c r="S36" t="n">
-        <v>667.4004755137141</v>
+        <v>1338.259295700009</v>
       </c>
       <c r="T36" t="n">
-        <v>454.0848739403684</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U36" t="n">
-        <v>450.8945448515577</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V36" t="n">
-        <v>433.2070022338605</v>
+        <v>1312.153197263404</v>
       </c>
       <c r="W36" t="n">
-        <v>55.42922445608272</v>
+        <v>1276.422749879739</v>
       </c>
       <c r="X36" t="n">
-        <v>32.33554824862055</v>
+        <v>1253.329073672277</v>
       </c>
       <c r="Y36" t="n">
-        <v>29.92</v>
+        <v>875.5512958944987</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>268.9900605843119</v>
+        <v>548.8299588860418</v>
       </c>
       <c r="C37" t="n">
-        <v>268.9900605843119</v>
+        <v>671.8619647044776</v>
       </c>
       <c r="D37" t="n">
-        <v>268.9900605843119</v>
+        <v>782.2111088294777</v>
       </c>
       <c r="E37" t="n">
-        <v>268.9900605843119</v>
+        <v>897.0700130408907</v>
       </c>
       <c r="F37" t="n">
-        <v>390.3810331762473</v>
+        <v>897.0700130408907</v>
       </c>
       <c r="G37" t="n">
-        <v>390.3810331762473</v>
+        <v>1048.161764173678</v>
       </c>
       <c r="H37" t="n">
-        <v>562.7528107946613</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="I37" t="n">
-        <v>800.618896943859</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="J37" t="n">
-        <v>812.0242344815562</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="K37" t="n">
-        <v>995.5392815331786</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="L37" t="n">
         <v>1066.665307034026</v>
@@ -7116,22 +7116,22 @@
         <v>75.61834706138623</v>
       </c>
       <c r="T37" t="n">
-        <v>263.5234540890435</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="U37" t="n">
-        <v>263.5234540890435</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="V37" t="n">
-        <v>268.9900605843119</v>
+        <v>271.4697399473322</v>
       </c>
       <c r="W37" t="n">
-        <v>268.9900605843119</v>
+        <v>440.3906582070096</v>
       </c>
       <c r="X37" t="n">
-        <v>268.9900605843119</v>
+        <v>440.3906582070096</v>
       </c>
       <c r="Y37" t="n">
-        <v>268.9900605843119</v>
+        <v>548.8299588860418</v>
       </c>
     </row>
     <row r="38">
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>117.1408562629478</v>
+        <v>113.806583727033</v>
       </c>
       <c r="C38" t="n">
-        <v>64.13623177507515</v>
+        <v>60.80195923916038</v>
       </c>
       <c r="D38" t="n">
-        <v>50.66233708835819</v>
+        <v>47.32806455244342</v>
       </c>
       <c r="E38" t="n">
-        <v>43.2246708187939</v>
+        <v>39.89039828287913</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889150919</v>
+        <v>31.92107635559443</v>
       </c>
       <c r="G38" t="n">
         <v>29.92</v>
@@ -7174,7 +7174,7 @@
         <v>535.4900049228883</v>
       </c>
       <c r="M38" t="n">
-        <v>739.431587554807</v>
+        <v>905.7500049228884</v>
       </c>
       <c r="N38" t="n">
         <v>1109.691587554807</v>
@@ -7192,25 +7192,25 @@
         <v>1496</v>
       </c>
       <c r="S38" t="n">
-        <v>1434.457487638385</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T38" t="n">
-        <v>1249.38969024747</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
-        <v>994.7399262092307</v>
+        <v>991.405653673316</v>
       </c>
       <c r="V38" t="n">
-        <v>759.5368714952672</v>
+        <v>756.2025989593525</v>
       </c>
       <c r="W38" t="n">
-        <v>515.7252795953201</v>
+        <v>512.3910070594054</v>
       </c>
       <c r="X38" t="n">
-        <v>318.4709023623224</v>
+        <v>315.1366298264077</v>
       </c>
       <c r="Y38" t="n">
-        <v>202.9987481372655</v>
+        <v>199.6644756013507</v>
       </c>
     </row>
     <row r="39">
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29.92</v>
+        <v>1047.352807281214</v>
       </c>
       <c r="C39" t="n">
-        <v>29.92</v>
+        <v>1047.352807281214</v>
       </c>
       <c r="D39" t="n">
-        <v>29.92</v>
+        <v>1047.352807281214</v>
       </c>
       <c r="E39" t="n">
-        <v>29.92</v>
+        <v>701.2193757439285</v>
       </c>
       <c r="F39" t="n">
-        <v>29.92</v>
+        <v>358.1524642915276</v>
       </c>
       <c r="G39" t="n">
         <v>29.92</v>
@@ -7268,28 +7268,28 @@
         <v>1422.95603106927</v>
       </c>
       <c r="R39" t="n">
-        <v>1045.178253291492</v>
+        <v>1320.671196754497</v>
       </c>
       <c r="S39" t="n">
-        <v>989.7223833062737</v>
+        <v>1134.698577557567</v>
       </c>
       <c r="T39" t="n">
-        <v>984.4941565761759</v>
+        <v>1129.47035082747</v>
       </c>
       <c r="U39" t="n">
-        <v>844.299679146683</v>
+        <v>1126.280021738659</v>
       </c>
       <c r="V39" t="n">
-        <v>466.5219013689052</v>
+        <v>1108.592479120962</v>
       </c>
       <c r="W39" t="n">
-        <v>430.79145398524</v>
+        <v>1072.862031737297</v>
       </c>
       <c r="X39" t="n">
-        <v>407.6977777777778</v>
+        <v>1049.768355529834</v>
       </c>
       <c r="Y39" t="n">
-        <v>29.92</v>
+        <v>1047.352807281214</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>461.4420370429931</v>
+        <v>326.2644077066896</v>
       </c>
       <c r="C40" t="n">
-        <v>461.4420370429931</v>
+        <v>326.2644077066896</v>
       </c>
       <c r="D40" t="n">
-        <v>461.4420370429931</v>
+        <v>326.2644077066896</v>
       </c>
       <c r="E40" t="n">
-        <v>461.4420370429931</v>
+        <v>326.2644077066896</v>
       </c>
       <c r="F40" t="n">
-        <v>461.4420370429931</v>
+        <v>447.6553802986251</v>
       </c>
       <c r="G40" t="n">
-        <v>461.4420370429931</v>
+        <v>447.6553802986251</v>
       </c>
       <c r="H40" t="n">
-        <v>461.4420370429931</v>
+        <v>512.890259982404</v>
       </c>
       <c r="I40" t="n">
-        <v>699.3081231921908</v>
+        <v>512.890259982404</v>
       </c>
       <c r="J40" t="n">
-        <v>1066.665307034026</v>
+        <v>883.150259982404</v>
       </c>
       <c r="K40" t="n">
         <v>1066.665307034026</v>
@@ -7356,19 +7356,19 @@
         <v>217.8251070276573</v>
       </c>
       <c r="U40" t="n">
-        <v>461.4420370429931</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="V40" t="n">
-        <v>461.4420370429931</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="W40" t="n">
-        <v>461.4420370429931</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="X40" t="n">
-        <v>461.4420370429931</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="Y40" t="n">
-        <v>461.4420370429931</v>
+        <v>326.2644077066896</v>
       </c>
     </row>
     <row r="41">
@@ -7402,25 +7402,25 @@
         <v>29.92</v>
       </c>
       <c r="J41" t="n">
-        <v>119.1959849731395</v>
+        <v>400.18</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113305</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228883</v>
+        <v>1000.937282311558</v>
       </c>
       <c r="M41" t="n">
-        <v>535.4900049228884</v>
+        <v>1000.937282311558</v>
       </c>
       <c r="N41" t="n">
-        <v>905.7500049228884</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O41" t="n">
-        <v>1082.303177009361</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P41" t="n">
-        <v>1292.058417368081</v>
+        <v>1496</v>
       </c>
       <c r="Q41" t="n">
         <v>1496</v>
@@ -7429,19 +7429,19 @@
         <v>1496</v>
       </c>
       <c r="S41" t="n">
-        <v>1496</v>
+        <v>1368.854228245085</v>
       </c>
       <c r="T41" t="n">
-        <v>1205.88169755858</v>
+        <v>1078.735925803665</v>
       </c>
       <c r="U41" t="n">
-        <v>846.1814284698353</v>
+        <v>719.0356567149207</v>
       </c>
       <c r="V41" t="n">
-        <v>505.9278687053667</v>
+        <v>378.7820969504521</v>
       </c>
       <c r="W41" t="n">
-        <v>157.0657717549146</v>
+        <v>29.92</v>
       </c>
       <c r="X41" t="n">
         <v>29.92</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.6172324016843</v>
+        <v>318.0281146697906</v>
       </c>
       <c r="C42" t="n">
-        <v>246.8294420526749</v>
+        <v>249.2403243207812</v>
       </c>
       <c r="D42" t="n">
         <v>191.3368290246924</v>
@@ -7484,49 +7484,49 @@
         <v>227.711345930016</v>
       </c>
       <c r="K42" t="n">
-        <v>250.1782010228462</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L42" t="n">
-        <v>460.3058139965494</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M42" t="n">
-        <v>744.4012057394086</v>
+        <v>599.927050901758</v>
       </c>
       <c r="N42" t="n">
-        <v>1080.937204214901</v>
+        <v>936.4630493772507</v>
       </c>
       <c r="O42" t="n">
-        <v>1451.197204214901</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P42" t="n">
         <v>1496</v>
       </c>
       <c r="Q42" t="n">
-        <v>1493.589117731894</v>
+        <v>1496</v>
       </c>
       <c r="R42" t="n">
-        <v>1286.253778366616</v>
+        <v>1288.664660634723</v>
       </c>
       <c r="S42" t="n">
-        <v>1125.747403330893</v>
+        <v>1128.158285598999</v>
       </c>
       <c r="T42" t="n">
-        <v>1015.46867155029</v>
+        <v>1017.879553818397</v>
       </c>
       <c r="U42" t="n">
-        <v>907.2278374109744</v>
+        <v>909.6387196790807</v>
       </c>
       <c r="V42" t="n">
-        <v>784.4897897427722</v>
+        <v>786.9006720108786</v>
       </c>
       <c r="W42" t="n">
-        <v>643.708837308602</v>
+        <v>646.1197195767083</v>
       </c>
       <c r="X42" t="n">
-        <v>515.5646560506348</v>
+        <v>517.9755383187411</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515092</v>
+        <v>410.5094850196155</v>
       </c>
     </row>
     <row r="43">
@@ -7569,22 +7569,22 @@
         <v>1163.052803794637</v>
       </c>
       <c r="M43" t="n">
-        <v>1163.052803794637</v>
+        <v>1160.444850760351</v>
       </c>
       <c r="N43" t="n">
-        <v>984.3546982875536</v>
+        <v>981.7467452532678</v>
       </c>
       <c r="O43" t="n">
-        <v>727.8873459308734</v>
+        <v>725.2793928965878</v>
       </c>
       <c r="P43" t="n">
-        <v>410.3057308120635</v>
+        <v>407.6977777777778</v>
       </c>
       <c r="Q43" t="n">
-        <v>88.34429643772449</v>
+        <v>29.92</v>
       </c>
       <c r="R43" t="n">
-        <v>88.34429643772449</v>
+        <v>29.92</v>
       </c>
       <c r="S43" t="n">
         <v>29.92</v>
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>140.3058539420142</v>
+        <v>334.652171053542</v>
       </c>
       <c r="C44" t="n">
-        <v>140.3058539420142</v>
+        <v>334.652171053542</v>
       </c>
       <c r="D44" t="n">
-        <v>140.3058539420142</v>
+        <v>334.652171053542</v>
       </c>
       <c r="E44" t="n">
-        <v>140.3058539420142</v>
+        <v>222.1639997334726</v>
       </c>
       <c r="F44" t="n">
-        <v>140.3058539420142</v>
+        <v>109.1441727556829</v>
       </c>
       <c r="G44" t="n">
         <v>29.92</v>
@@ -7642,13 +7642,13 @@
         <v>119.1959849731395</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113305</v>
+        <v>489.4559849731395</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228883</v>
+        <v>719.9532672846973</v>
       </c>
       <c r="M44" t="n">
-        <v>739.4315875548016</v>
+        <v>1090.213267284697</v>
       </c>
       <c r="N44" t="n">
         <v>1109.691587554807</v>
@@ -7666,25 +7666,25 @@
         <v>1496</v>
       </c>
       <c r="S44" t="n">
-        <v>1496</v>
+        <v>1326.072710051965</v>
       </c>
       <c r="T44" t="n">
-        <v>1496</v>
+        <v>1326.072710051965</v>
       </c>
       <c r="U44" t="n">
-        <v>1352.249052216</v>
+        <v>1326.072710051965</v>
       </c>
       <c r="V44" t="n">
-        <v>1011.995492451531</v>
+        <v>985.8191502874969</v>
       </c>
       <c r="W44" t="n">
-        <v>663.1333955010789</v>
+        <v>636.9570533370447</v>
       </c>
       <c r="X44" t="n">
-        <v>360.8285132175762</v>
+        <v>334.652171053542</v>
       </c>
       <c r="Y44" t="n">
-        <v>140.3058539420142</v>
+        <v>334.652171053542</v>
       </c>
     </row>
     <row r="45">
@@ -7724,16 +7724,16 @@
         <v>543.0996394772296</v>
       </c>
       <c r="L45" t="n">
-        <v>599.927050901758</v>
+        <v>784.4390741634611</v>
       </c>
       <c r="M45" t="n">
-        <v>884.0224426446173</v>
+        <v>1068.53446590632</v>
       </c>
       <c r="N45" t="n">
-        <v>1188.111259659669</v>
+        <v>1405.070464381813</v>
       </c>
       <c r="O45" t="n">
-        <v>1234.237999492757</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P45" t="n">
         <v>1496</v>
@@ -7806,19 +7806,19 @@
         <v>1130.57247066623</v>
       </c>
       <c r="M46" t="n">
-        <v>1005.430107765823</v>
+        <v>1130.57247066623</v>
       </c>
       <c r="N46" t="n">
-        <v>826.7320022587398</v>
+        <v>951.8743651591462</v>
       </c>
       <c r="O46" t="n">
-        <v>570.2646499020598</v>
+        <v>695.4070128024662</v>
       </c>
       <c r="P46" t="n">
-        <v>252.6830347832499</v>
+        <v>377.8253976836563</v>
       </c>
       <c r="Q46" t="n">
-        <v>252.6830347832499</v>
+        <v>377.8253976836563</v>
       </c>
       <c r="R46" t="n">
         <v>88.34429643772452</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>707.7620966723902</v>
+        <v>714.2808456769349</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8219,10 +8219,10 @@
         <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>235.7417089435049</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
         <v>321.8400703517588</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>707.7620966723902</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>382.6480632645622</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M11" t="n">
-        <v>940.1988562855347</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N11" t="n">
-        <v>868.9937721401884</v>
+        <v>414.7873509852764</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>382.6480632645602</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855356</v>
       </c>
       <c r="N14" t="n">
-        <v>827.6248783961064</v>
+        <v>868.9937721401893</v>
       </c>
       <c r="O14" t="n">
-        <v>476.6634625389187</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,16 +9149,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>433.3459296003462</v>
+        <v>290.1886884942116</v>
       </c>
       <c r="N17" t="n">
         <v>868.9937721401902</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>467.326527638191</v>
+        <v>467.3265276381908</v>
       </c>
       <c r="L20" t="n">
-        <v>422.1744623115576</v>
+        <v>192.6633045704907</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855374</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N20" t="n">
-        <v>362.1408454549988</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>382.6480632645547</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>940.1988562855383</v>
+        <v>940.1988562855374</v>
       </c>
       <c r="N23" t="n">
-        <v>868.993772140192</v>
+        <v>784.3153077665565</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,16 +9863,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>467.3265276381908</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>422.1744623115578</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>658.0411930141927</v>
+        <v>940.1988562855347</v>
       </c>
       <c r="N26" t="n">
-        <v>213.993772140187</v>
+        <v>821.3370988185936</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>467.3265276381908</v>
+        <v>382.6480632645622</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>477.8621608560239</v>
+        <v>940.1988562855347</v>
       </c>
       <c r="N29" t="n">
-        <v>213.993772140187</v>
+        <v>868.9937721401884</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>382.6480632645524</v>
+        <v>382.6480632645622</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>940.1988562855395</v>
+        <v>940.1988562855347</v>
       </c>
       <c r="N32" t="n">
-        <v>868.993772140193</v>
+        <v>868.9937721401884</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>491.200454903633</v>
+        <v>659.1988562855333</v>
       </c>
       <c r="N35" t="n">
-        <v>587.993772140187</v>
+        <v>419.9953707582866</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10650,19 +10650,19 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>27.675503614641</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>167.0143075450254</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>452.633596403228</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>491.200454903633</v>
+        <v>659.1988562855333</v>
       </c>
       <c r="N38" t="n">
-        <v>587.993772140187</v>
+        <v>419.9953707582866</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>283.8222374008692</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>186.3265276381909</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N41" t="n">
-        <v>587.993772140187</v>
+        <v>323.8466057192267</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>219.5001774179469</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,22 +11127,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>154.8486884335099</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>327.4073335019309</v>
+        <v>254.1901113963821</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>186.326527638191</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>491.2004549036276</v>
+        <v>659.1988562855333</v>
       </c>
       <c r="N44" t="n">
-        <v>587.9937721401925</v>
+        <v>233.6688431200957</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11367,19 +11367,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>186.3757810724275</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>452.633596403228</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.458477865729947e-12</v>
+        <v>5.968558980384842e-13</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -23472,10 +23472,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.850361477466563</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24000,7 +24000,7 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -24125,7 +24125,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.850361477466308</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24228,13 +24228,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6960849964950739</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85036147746635</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.6960849964949603</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85036147746635</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.6960849964949603</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
     </row>
     <row r="30">
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.850361477466352</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -25088,10 +25088,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="S34" t="n">
-        <v>2.85036147746635</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>3.300929810555616</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.300929810555573</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3.300929810555617</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.300929810555573</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>42.35370301118853</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>173.4075194233023</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>218.3174326828064</v>
@@ -25784,7 +25784,7 @@
         <v>32.15552979712344</v>
       </c>
       <c r="M43" t="n">
-        <v>123.8909392714024</v>
+        <v>121.3090657674594</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -25796,13 +25796,13 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>58.68044639500238</v>
+        <v>3.422266425597996</v>
       </c>
       <c r="R43" t="n">
         <v>403.845046013938</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25839,13 +25839,13 @@
         <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>30.85006437446805</v>
       </c>
       <c r="H44" t="n">
         <v>99.89995518593946</v>
@@ -25881,13 +25881,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>213.7898280916966</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -26021,7 +26021,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>377.422266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>241.1496950518678</v>
+        <v>117.2587557804655</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26275,7 +26275,7 @@
         <v>1164923.76230765</v>
       </c>
       <c r="D2" t="n">
-        <v>1164923.762307649</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="E2" t="n">
         <v>1164809.231544557</v>
@@ -26284,19 +26284,19 @@
         <v>1164809.231544557</v>
       </c>
       <c r="G2" t="n">
+        <v>1164809.231544559</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1164809.231544559</v>
+      </c>
+      <c r="I2" t="n">
         <v>1164809.231544558</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1164809.231544558</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1164809.231544557</v>
       </c>
       <c r="J2" t="n">
         <v>1164809.231544557</v>
       </c>
       <c r="K2" t="n">
-        <v>1164809.231544558</v>
+        <v>1164809.231544557</v>
       </c>
       <c r="L2" t="n">
         <v>1164809.231544557</v>
@@ -26305,7 +26305,7 @@
         <v>1164680.714845699</v>
       </c>
       <c r="N2" t="n">
-        <v>1164680.714845698</v>
+        <v>1164680.714845699</v>
       </c>
       <c r="O2" t="n">
         <v>1044045.023600558</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101185</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687438</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432671</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027683</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045217</v>
+        <v>499902.9383787896</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.75052655</v>
+        <v>498222.5921008178</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963753</v>
+        <v>496539.8583706432</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842147</v>
+        <v>522371.0444804642</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731494</v>
+        <v>520403.913769399</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155932</v>
+        <v>447670.9673118427</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523478</v>
+        <v>446003.2126485973</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>272816.1860975319</v>
+        <v>273015.5007527462</v>
       </c>
       <c r="C6" t="n">
-        <v>505923.10828502</v>
+        <v>506122.4229402348</v>
       </c>
       <c r="D6" t="n">
-        <v>507934.7557008433</v>
+        <v>508134.0703560589</v>
       </c>
       <c r="E6" t="n">
-        <v>-30783.99692402393</v>
+        <v>-30589.83849829176</v>
       </c>
       <c r="F6" t="n">
-        <v>583371.6685758133</v>
+        <v>583565.8270015452</v>
       </c>
       <c r="G6" t="n">
-        <v>585042.6367714349</v>
+        <v>585236.7951971676</v>
       </c>
       <c r="H6" t="n">
-        <v>586715.9241755588</v>
+        <v>586910.0826012915</v>
       </c>
       <c r="I6" t="n">
-        <v>588391.5475160563</v>
+        <v>588585.7059417901</v>
       </c>
       <c r="J6" t="n">
-        <v>203221.523740035</v>
+        <v>203415.6821657674</v>
       </c>
       <c r="K6" t="n">
-        <v>591749.8700180082</v>
+        <v>591944.0284437391</v>
       </c>
       <c r="L6" t="n">
-        <v>593432.6037481811</v>
+        <v>593626.7621739134</v>
       </c>
       <c r="M6" t="n">
-        <v>515675.0602614839</v>
+        <v>515794.4773652349</v>
       </c>
       <c r="N6" t="n">
-        <v>580042.1909725489</v>
+        <v>580161.6080762995</v>
       </c>
       <c r="O6" t="n">
-        <v>368882.6221849647</v>
+        <v>369002.0392887151</v>
       </c>
       <c r="P6" t="n">
-        <v>542550.37684821</v>
+        <v>542669.7939519605</v>
       </c>
     </row>
   </sheetData>
@@ -26978,7 +26978,7 @@
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>319</v>
@@ -26987,7 +26987,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27002,7 +27002,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>78</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095032979</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.2013121321728</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27521,13 +27521,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,16 +27569,16 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>78.01946960411124</v>
+        <v>227.1478262079978</v>
       </c>
       <c r="V3" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27594,16 +27594,16 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>300.1266501728634</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>244.8599384153005</v>
@@ -27612,7 +27612,7 @@
         <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>308.5518289361902</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
         <v>22.26478490148153</v>
@@ -27648,7 +27648,7 @@
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27685,13 +27685,13 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>398.2013121321734</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033002</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>204.2115150049544</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>334.2798153697952</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27849,13 +27849,13 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>349.2746269966813</v>
       </c>
       <c r="J7" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
         <v>396.2015953708939</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
-        <v>289.2544988437064</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321734</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I8" t="n">
         <v>134.2726973711268</v>
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77.08669344195846</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>295.3942944519113</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28080,22 +28080,22 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>376.5799194282308</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28119,22 +28119,22 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>399.8430263534097</v>
       </c>
       <c r="U10" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28238,10 +28238,10 @@
         <v>319</v>
       </c>
       <c r="G12" t="n">
-        <v>96.05772723972424</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>189.9476123064429</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -28277,7 +28277,7 @@
         <v>319</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>168.3712564811472</v>
       </c>
       <c r="U12" t="n">
         <v>319</v>
@@ -28286,13 +28286,13 @@
         <v>319</v>
       </c>
       <c r="W12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>319</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
@@ -28460,16 +28460,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C15" t="n">
-        <v>168.3712564811478</v>
+        <v>319</v>
       </c>
       <c r="D15" t="n">
         <v>319</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F15" t="n">
         <v>319</v>
@@ -28478,7 +28478,7 @@
         <v>319</v>
       </c>
       <c r="H15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>189.9476123064429</v>
@@ -28505,10 +28505,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R15" t="n">
-        <v>319</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="S15" t="n">
         <v>319</v>
@@ -28517,10 +28517,10 @@
         <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W15" t="n">
         <v>319</v>
@@ -28529,7 +28529,7 @@
         <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28700,16 +28700,16 @@
         <v>319</v>
       </c>
       <c r="C18" t="n">
-        <v>96.05772723972427</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>319</v>
@@ -28757,16 +28757,16 @@
         <v>319</v>
       </c>
       <c r="V18" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="W18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28934,10 +28934,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>319</v>
@@ -28952,7 +28952,7 @@
         <v>319</v>
       </c>
       <c r="H21" t="n">
-        <v>168.3712564811475</v>
+        <v>319</v>
       </c>
       <c r="I21" t="n">
         <v>189.9476123064429</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="S21" t="n">
         <v>319</v>
@@ -28994,16 +28994,16 @@
         <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X21" t="n">
-        <v>319</v>
+        <v>96.05772723972456</v>
       </c>
       <c r="Y21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29174,16 +29174,16 @@
         <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29216,10 +29216,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
-        <v>168.3712564811473</v>
+        <v>319</v>
       </c>
       <c r="S24" t="n">
         <v>319</v>
@@ -29231,16 +29231,16 @@
         <v>319</v>
       </c>
       <c r="V24" t="n">
-        <v>319</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="W24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>319</v>
       </c>
       <c r="Y24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29411,7 +29411,7 @@
         <v>319</v>
       </c>
       <c r="C27" t="n">
-        <v>319</v>
+        <v>168.3712564811474</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>319</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>319</v>
@@ -29468,10 +29468,10 @@
         <v>319</v>
       </c>
       <c r="V27" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X27" t="n">
         <v>319</v>
@@ -29657,13 +29657,13 @@
         <v>319</v>
       </c>
       <c r="F30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="H30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>189.9476123064429</v>
@@ -29693,16 +29693,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>168.3712564811476</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="T30" t="n">
-        <v>168.3712564811474</v>
+        <v>319</v>
       </c>
       <c r="U30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>319</v>
@@ -29885,19 +29885,19 @@
         <v>319</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D33" t="n">
         <v>319</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>319</v>
@@ -29927,13 +29927,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>96.05772723972439</v>
+        <v>319</v>
       </c>
       <c r="S33" t="n">
-        <v>319</v>
+        <v>168.3712564811476</v>
       </c>
       <c r="T33" t="n">
         <v>319</v>
@@ -29942,13 +29942,13 @@
         <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>319</v>
       </c>
       <c r="X33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>319</v>
@@ -30131,13 +30131,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9501396486123</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>324.5441815260438</v>
+        <v>151.9555805769793</v>
       </c>
       <c r="I36" t="n">
         <v>189.9476123064429</v>
@@ -30164,16 +30164,16 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
-        <v>124.2619859716246</v>
+        <v>397</v>
       </c>
       <c r="S36" t="n">
-        <v>77.90131128536602</v>
+        <v>397</v>
       </c>
       <c r="T36" t="n">
-        <v>190.9934989051845</v>
+        <v>397</v>
       </c>
       <c r="U36" t="n">
         <v>397</v>
@@ -30182,13 +30182,13 @@
         <v>397</v>
       </c>
       <c r="W36" t="n">
-        <v>58.37314290982852</v>
+        <v>397</v>
       </c>
       <c r="X36" t="n">
         <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>397</v>
+        <v>25.39139276613437</v>
       </c>
     </row>
     <row r="37">
@@ -30201,34 +30201,34 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>397</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F37" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G37" t="n">
         <v>397</v>
       </c>
-      <c r="G37" t="n">
-        <v>244.3820695628415</v>
-      </c>
       <c r="H37" t="n">
-        <v>397</v>
+        <v>230.0569976810482</v>
       </c>
       <c r="I37" t="n">
-        <v>397</v>
+        <v>156.7312261119215</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>397</v>
+        <v>211.6312656044217</v>
       </c>
       <c r="L37" t="n">
-        <v>397</v>
+        <v>325.1555297971234</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30252,22 +30252,22 @@
         <v>397</v>
       </c>
       <c r="T37" t="n">
-        <v>397</v>
+        <v>207.1968615882249</v>
       </c>
       <c r="U37" t="n">
         <v>150.9222929138022</v>
       </c>
       <c r="V37" t="n">
-        <v>204.6921349589115</v>
+        <v>397</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>397</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>397</v>
       </c>
     </row>
     <row r="38">
@@ -30365,13 +30365,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9501396486123</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>324.5441815260438</v>
@@ -30404,19 +30404,19 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>124.2619859716246</v>
+        <v>397</v>
       </c>
       <c r="S39" t="n">
-        <v>397</v>
+        <v>267.7884182804053</v>
       </c>
       <c r="T39" t="n">
         <v>397</v>
       </c>
       <c r="U39" t="n">
-        <v>261.3658931427246</v>
+        <v>397</v>
       </c>
       <c r="V39" t="n">
-        <v>40.51066719152016</v>
+        <v>397</v>
       </c>
       <c r="W39" t="n">
         <v>397</v>
@@ -30425,7 +30425,7 @@
         <v>397</v>
       </c>
       <c r="Y39" t="n">
-        <v>25.39139276613435</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40">
@@ -30447,22 +30447,22 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G40" t="n">
         <v>244.3820695628415</v>
       </c>
       <c r="H40" t="n">
-        <v>222.8870933147334</v>
+        <v>288.7809111771363</v>
       </c>
       <c r="I40" t="n">
+        <v>156.7312261119215</v>
+      </c>
+      <c r="J40" t="n">
+        <v>362.4794570326291</v>
+      </c>
+      <c r="K40" t="n">
         <v>397</v>
-      </c>
-      <c r="J40" t="n">
-        <v>359.5473194991298</v>
-      </c>
-      <c r="K40" t="n">
-        <v>211.6312656044217</v>
       </c>
       <c r="L40" t="n">
         <v>325.1555297971234</v>
@@ -30492,7 +30492,7 @@
         <v>397</v>
       </c>
       <c r="U40" t="n">
-        <v>397</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V40" t="n">
         <v>199.1703102162162</v>
@@ -30504,7 +30504,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41">
@@ -30599,7 +30599,7 @@
         <v>293</v>
       </c>
       <c r="D42" t="n">
-        <v>293</v>
+        <v>290.6132265545748</v>
       </c>
       <c r="E42" t="n">
         <v>293</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>69.92675579599782</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R42" t="n">
         <v>293</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L2" t="n">
+        <v>64.70900502512562</v>
+      </c>
+      <c r="M2" t="n">
+        <v>242.0199542155221</v>
+      </c>
+      <c r="N2" t="n">
         <v>374</v>
       </c>
-      <c r="K2" t="n">
-        <v>373.9999999999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>64.70900502512563</v>
-      </c>
-      <c r="M2" t="n">
-        <v>235.5012052109774</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,16 +34880,16 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>27.40140352481872</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -34898,7 +34898,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>137.4497831521375</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34934,7 +34934,7 @@
         <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>235.5012052109774</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
         <v>64.70900502512563</v>
@@ -34998,10 +34998,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>242.0199542155222</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35135,13 +35135,13 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>178.1725812126285</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698063</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>80.01583397679292</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>374</v>
@@ -35226,10 +35226,10 @@
         <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
+        <v>235.5012052109774</v>
+      </c>
+      <c r="N8" t="n">
         <v>374</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35366,22 +35366,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>131.7199810129302</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,22 +35405,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.6043614864962</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,16 +35457,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K11" t="n">
-        <v>570.3215356263712</v>
+        <v>655</v>
       </c>
       <c r="L11" t="n">
-        <v>232.8255376884422</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>655.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>655.0000000000013</v>
+        <v>200.7935788450894</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35475,7 +35475,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,25 +35694,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K14" t="n">
-        <v>187.673472361809</v>
+        <v>570.3215356263692</v>
       </c>
       <c r="L14" t="n">
         <v>232.8255376884423</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="N14" t="n">
-        <v>613.6311062559193</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="O14" t="n">
-        <v>655.0000000000022</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P14" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,16 +35928,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K17" t="n">
-        <v>655</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L17" t="n">
-        <v>654.9999999999999</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M17" t="n">
-        <v>148.1470733148128</v>
+        <v>4.989832208678244</v>
       </c>
       <c r="N17" t="n">
         <v>655.0000000000031</v>
@@ -35949,7 +35949,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
-        <v>655</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>654.9999999999999</v>
+        <v>425.4888422589329</v>
       </c>
       <c r="M20" t="n">
-        <v>655.000000000004</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>148.1470733148118</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36186,7 +36186,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36405,16 +36405,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K23" t="n">
-        <v>570.3215356263636</v>
+        <v>655</v>
       </c>
       <c r="L23" t="n">
-        <v>232.8255376884424</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M23" t="n">
-        <v>655.0000000000049</v>
+        <v>655.000000000004</v>
       </c>
       <c r="N23" t="n">
-        <v>655.0000000000049</v>
+        <v>570.3215356263696</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36563,7 +36563,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K25" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36642,16 +36642,16 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K26" t="n">
-        <v>654.9999999999999</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L26" t="n">
-        <v>655</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M26" t="n">
-        <v>372.8423367286592</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>607.3433266784065</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
-        <v>654.9999999999999</v>
+        <v>570.3215356263712</v>
       </c>
       <c r="L29" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M29" t="n">
-        <v>192.6633045704905</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
@@ -36897,7 +36897,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37076,7 +37076,7 @@
         <v>92.62719016129032</v>
       </c>
       <c r="X31" t="n">
-        <v>71.55635456989246</v>
+        <v>71.55635456989245</v>
       </c>
       <c r="Y31" t="n">
         <v>31.53464715053764</v>
@@ -37116,16 +37116,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
-        <v>570.3215356263614</v>
+        <v>570.3215356263712</v>
       </c>
       <c r="L32" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M32" t="n">
-        <v>655.000000000006</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="N32" t="n">
-        <v>655.000000000006</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37359,10 +37359,10 @@
         <v>232.8255376884423</v>
       </c>
       <c r="M35" t="n">
+        <v>374</v>
+      </c>
+      <c r="N35" t="n">
         <v>206.0015986180996</v>
-      </c>
-      <c r="N35" t="n">
-        <v>374</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37429,19 +37429,19 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K36" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>224.4157332263671</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M36" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>339.9353519954473</v>
+        <v>307.160421227325</v>
       </c>
       <c r="O36" t="n">
         <v>46.59266649806909</v>
@@ -37487,34 +37487,34 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>122.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>152.6179304371585</v>
       </c>
       <c r="H37" t="n">
-        <v>174.1129066852666</v>
+        <v>7.169904366314814</v>
       </c>
       <c r="I37" t="n">
-        <v>240.2687738880785</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>11.52054296737091</v>
       </c>
       <c r="K37" t="n">
-        <v>185.3687343955783</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>71.84447020287656</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37538,22 +37538,22 @@
         <v>46.15994652665276</v>
       </c>
       <c r="T37" t="n">
-        <v>189.8031384117751</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.521824742695319</v>
+        <v>197.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>109.5346471505376</v>
       </c>
     </row>
     <row r="38">
@@ -37596,10 +37596,10 @@
         <v>232.8255376884423</v>
       </c>
       <c r="M38" t="n">
+        <v>374</v>
+      </c>
+      <c r="N38" t="n">
         <v>206.0015986180996</v>
-      </c>
-      <c r="N38" t="n">
-        <v>374</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
@@ -37733,22 +37733,22 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>65.89381786240293</v>
       </c>
       <c r="I40" t="n">
-        <v>240.2687738880785</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>371.0678624665007</v>
+        <v>374</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>185.3687343955783</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37778,7 +37778,7 @@
         <v>189.8031384117751</v>
       </c>
       <c r="U40" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -37790,7 +37790,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>109.5346471505376</v>
       </c>
     </row>
     <row r="41">
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>90.1777625991308</v>
+        <v>374</v>
       </c>
       <c r="K41" t="n">
-        <v>187.673472361809</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>374</v>
+        <v>109.8528335790397</v>
       </c>
       <c r="O41" t="n">
         <v>178.3365374610834</v>
@@ -37845,7 +37845,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q41" t="n">
-        <v>206.0015986180996</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,22 +37906,22 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K42" t="n">
-        <v>22.69379302306083</v>
+        <v>318.5740338860743</v>
       </c>
       <c r="L42" t="n">
-        <v>212.2501141148517</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M42" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>374</v>
+        <v>300.7827778944511</v>
       </c>
       <c r="P42" t="n">
-        <v>45.25534927787736</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38064,16 +38064,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K44" t="n">
-        <v>187.673472361809</v>
+        <v>374</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M44" t="n">
-        <v>206.0015986180942</v>
+        <v>374</v>
       </c>
       <c r="N44" t="n">
-        <v>374.0000000000055</v>
+        <v>19.67507097990872</v>
       </c>
       <c r="O44" t="n">
         <v>178.3365374610834</v>
@@ -38146,19 +38146,19 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L45" t="n">
-        <v>57.40142568134173</v>
+        <v>243.7772067537692</v>
       </c>
       <c r="M45" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>307.160421227325</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
         <v>46.59266649806909</v>
       </c>
       <c r="P45" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
